--- a/bar_trivia_geography_fine_art.xlsx
+++ b/bar_trivia_geography_fine_art.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sources" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trivia'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trivia'!$A$1:$E$251</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,25 +84,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,13 +478,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +506,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Wrong Answers (Multiple Choice)</t>
         </is>
       </c>
@@ -491,7 +521,7 @@
           <t>What is the largest ocean in the world?</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Pacific Ocean</t>
         </is>
@@ -501,7 +531,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -509,7 +544,7 @@
           <t>What is the tallest mountain range in the world?</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Himalayas</t>
         </is>
@@ -519,7 +554,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -527,7 +567,7 @@
           <t>What is the world's southernmost continent?</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Antarctica</t>
         </is>
@@ -537,7 +577,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -545,7 +590,7 @@
           <t>What continent is also a country?</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
@@ -555,7 +600,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -563,7 +613,7 @@
           <t>What country has the longest coastline in the world?</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
@@ -573,7 +623,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -581,7 +636,7 @@
           <t>What two countries share the longest international border?</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Canada and the United States</t>
         </is>
@@ -591,7 +646,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -599,7 +659,7 @@
           <t>Which continent has the most countries?</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Africa</t>
         </is>
@@ -609,7 +669,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -617,7 +682,7 @@
           <t>What is the smallest country in the world by land area?</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Vatican City</t>
         </is>
@@ -627,7 +692,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -635,7 +705,7 @@
           <t>What two countries are doubly landlocked (surrounded only by landlocked countries)?</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Liechtenstein and Uzbekistan</t>
         </is>
@@ -645,7 +715,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -653,7 +728,7 @@
           <t>What African country has the highest population?</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
@@ -663,7 +738,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -671,7 +751,7 @@
           <t>How many countries are there in Africa?</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="6" t="n">
         <v>54</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -679,7 +759,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -687,7 +772,7 @@
           <t>How many countries sit on the equator?</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="6" t="n">
         <v>13</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -695,7 +780,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -703,7 +793,7 @@
           <t>How many recognized countries are there in the world?</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>195</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -711,7 +801,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -719,7 +814,7 @@
           <t>Which country in South America is the smallest by land area?</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Suriname</t>
         </is>
@@ -729,7 +824,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -737,7 +837,7 @@
           <t>Which river flows through the most countries?</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Danube</t>
         </is>
@@ -747,7 +847,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -755,7 +860,7 @@
           <t>How many countries does the Danube River flow through?</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="6" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -763,7 +868,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -771,7 +881,7 @@
           <t>Which river has the largest water discharge in the world?</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Amazon River</t>
         </is>
@@ -781,7 +891,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -789,7 +904,7 @@
           <t>What is the longest river in Europe?</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Volga River</t>
         </is>
@@ -799,7 +914,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -807,7 +927,7 @@
           <t>What is the world's deepest lake?</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Lake Baikal</t>
         </is>
@@ -817,7 +937,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -825,7 +950,7 @@
           <t>Which African lake is the world's longest freshwater lake and second deepest freshwater lake?</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Lake Tanganyika</t>
         </is>
@@ -835,7 +960,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -843,7 +973,7 @@
           <t>Which country is home to the Okavango Delta, the world's largest inland delta?</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Botswana</t>
         </is>
@@ -853,7 +983,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -861,7 +996,7 @@
           <t>What is the capital of Australia?</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Canberra</t>
         </is>
@@ -871,7 +1006,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -879,7 +1019,7 @@
           <t>How tall is Mount Everest, in meters?</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="7" t="n">
         <v>8849</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -887,7 +1027,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -895,7 +1040,7 @@
           <t>How long is the border between Canada and the USA, in kilometers?</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="7" t="n">
         <v>8891</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -903,7 +1048,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -911,7 +1061,7 @@
           <t>In which Australian archipelago can you find Whitehaven Beach?</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Whitsunday Islands</t>
         </is>
@@ -921,7 +1071,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -929,7 +1084,7 @@
           <t>Who painted the Mona Lisa?</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Leonardo da Vinci</t>
         </is>
@@ -939,7 +1094,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -947,7 +1107,7 @@
           <t>Which artist famously cut off part of his own ear?</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Vincent van Gogh</t>
         </is>
@@ -957,7 +1117,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -965,7 +1130,7 @@
           <t>Which artist painted the melting clocks in The Persistence of Memory?</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Salvador Dalí</t>
         </is>
@@ -975,7 +1140,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -983,7 +1153,7 @@
           <t>Which artist painted Girl with a Pearl Earring?</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Johannes Vermeer</t>
         </is>
@@ -993,7 +1163,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1001,7 +1176,7 @@
           <t>What artistic movement is Claude Monet most closely associated with?</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Impressionism</t>
         </is>
@@ -1011,7 +1186,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1019,7 +1199,7 @@
           <t>Which artist painted Las Meninas?</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Diego Velázquez</t>
         </is>
@@ -1029,7 +1209,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1037,7 +1222,7 @@
           <t>Who painted the ceiling of the Sistine Chapel?</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Michelangelo</t>
         </is>
@@ -1047,7 +1232,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1055,7 +1245,7 @@
           <t>Which artist created the sculpture The Thinker?</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Auguste Rodin</t>
         </is>
@@ -1065,7 +1255,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1073,7 +1268,7 @@
           <t>What is the name for Michelangelo's 1499 sculpture of the Virgin Mary cradling the body of Jesus?</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Pietà</t>
         </is>
@@ -1083,7 +1278,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1091,7 +1291,7 @@
           <t>Which Italian sculptor created the bronze David and the Equestrian Statue of Gattamelata?</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Donatello</t>
         </is>
@@ -1101,7 +1301,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1109,7 +1314,7 @@
           <t>What style of art features unnerving, illogical, dreamlike scenes painted with photographic precision?</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Surrealism</t>
         </is>
@@ -1119,7 +1324,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1127,7 +1337,7 @@
           <t>Henri Matisse led which early-20th-century movement whose name comes from the French for "wild beasts"?</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Fauvism</t>
         </is>
@@ -1137,7 +1347,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1145,7 +1360,7 @@
           <t>What 20th-century movement, founded by Kazimir Malevich, reduced art to pure geometric abstraction?</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Suprematism</t>
         </is>
@@ -1155,7 +1370,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1163,7 +1383,7 @@
           <t>Which museum is home to the Mona Lisa?</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>The Louvre</t>
         </is>
@@ -1173,7 +1393,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1181,7 +1406,7 @@
           <t>Which artist painted American Gothic?</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Grant Wood</t>
         </is>
@@ -1191,7 +1416,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1199,7 +1429,7 @@
           <t>Which artist painted the Water Lilies series?</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Claude Monet</t>
         </is>
@@ -1209,7 +1439,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1217,7 +1452,7 @@
           <t>Who painted Guernica, the famous anti-war mural?</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Pablo Picasso</t>
         </is>
@@ -1227,7 +1462,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1235,7 +1475,7 @@
           <t>How many still-life paintings of sunflowers did Van Gogh create between 1887 and 1889?</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
+      <c r="B44" s="6" t="n">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1243,7 +1483,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1251,7 +1496,7 @@
           <t>How many versions of Sunflowers did Van Gogh paint in Arles?</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B45" s="6" t="n">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1259,7 +1504,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1267,7 +1517,7 @@
           <t>Van Gogh painted his Arles Sunflowers to decorate his house for a visit from which fellow artist?</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Paul Gauguin</t>
         </is>
@@ -1277,7 +1527,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1285,7 +1540,7 @@
           <t>In what year did Van Gogh paint The Starry Night?</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>1889</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1293,7 +1548,12 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1301,7 +1561,7 @@
           <t>Who painted The Scream?</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Edvard Munch</t>
         </is>
@@ -1311,7 +1571,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1319,7 +1584,7 @@
           <t>Who painted The Birth of Venus?</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Sandro Botticelli</t>
         </is>
@@ -1329,7 +1594,12 @@
           <t>phrase</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1337,7 +1607,7 @@
           <t>Which Dutch Golden Age painter created The Night Watch?</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Rembrandt</t>
         </is>
@@ -1347,7 +1617,12 @@
           <t>word</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1355,7 +1630,7 @@
           <t>In what year did Rembrandt paint The Night Watch?</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>1642</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1363,10 +1638,4569 @@
           <t>number</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Mexico?</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Spain?</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Egypt?</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Norway?</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Ireland?</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Canada?</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Ottawa</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Japan?</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Russia?</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Italy?</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of France?</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of New Zealand?</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Wellington</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria moved its capital from Lagos to which city?</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Abuja</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Kazakhstan (it briefly went by Nur-Sultan)?</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Astana</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>What is the capital of Myanmar (not Yangon)?</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Naypyidaw</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>In which country is Machu Picchu located?</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>What country is home to the Pyramids of Giza?</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>In which country is the Taj Mahal located?</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Which country would you visit to see the Colosseum?</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Which country is famous for the Eiffel Tower?</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>In which American city is the Golden Gate Bridge located?</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest U.S. state by area?</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Which is the only U.S. state made up entirely of islands?</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>What is the highest mountain in the world above sea level?</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Mount Everest</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>What is the highest mountain in Africa?</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Mount Kilimanjaro</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>On which continent is the Sahara Desert located?</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>What is the longest river in the world?</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Nile</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest lake in Africa?</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Lake Victoria</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest island in the world?</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Greenland</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest country in South America?</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest country in the world by land area?</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through Paris?</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Seine</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through London?</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Thames</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>How many states are in the United States?</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>How many oceans are there on Earth?</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>What is the smallest and shallowest of the world's oceans?</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Arctic Ocean</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Which Asian country is known as the "Land of the Rising Sun"?</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Which mountain range runs along the western coast of South America?</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Andes</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>If you travel from Beijing to Tokyo, which compass direction are you mainly heading?</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Name all five Great Lakes.</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Superior, Michigan, Huron, Erie, Ontario</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>What is the name of the peninsula shared by Spain and Portugal?</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Iberian Peninsula</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Which mountain range is traditionally considered the boundary between Europe and Asia?</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Ural Mountains</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Which European country is nicknamed "The Land of a Thousand Lakes"?</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Counting its fjords and islands, which country has the longest coastline in Europe?</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>What is the most populous city in Scotland?</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Which Tuscan city on the Arno River is called the birthplace of the Renaissance?</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Which Caribbean island is shared by Haiti and the Dominican Republic?</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Hispaniola</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Which peninsula separates the Gulf of Mexico from the Caribbean Sea?</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Yucatán Peninsula</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>What is the longest river in Asia?</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Yangtze</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Which desert stretches across northern China and southern Mongolia?</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Gobi</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Which country has the most volcanoes?</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>What is the second-highest mountain in the world?</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>What is the tallest mountain in North America (formerly Mount McKinley)?</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Denali</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>What is the driest non-polar desert in the world, located in Chile?</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Atacama Desert</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Which U.S. state has the most volcanoes?</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>What is the second-largest island in the world, split between Indonesia and Papua New Guinea?</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>New Guinea</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest island in the Mediterranean Sea?</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Sicily</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>What is the largest of Spain's Balearic Islands?</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Majorca</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>What are the giant stone statues on Easter Island called?</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Moai</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Which Indian Ocean nation is made up of coral atolls and is the lowest-lying country in the world?</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Maldives</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Which strait separates Spain from Morocco?</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Gibraltar</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Which strait separates Asia from North America?</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Bering Strait</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Which strait, named for a 16th-century explorer, separates mainland South America from Tierra del Fuego?</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Magellan</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Which strait between the Malay Peninsula and Sumatra links the Indian and Pacific Oceans?</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Malacca</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Which strait links the Persian Gulf with the Gulf of Oman?</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Strait of Hormuz</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Which strait separates the North and South Islands of New Zealand?</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Cook Strait</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>The isthmus of which country connects Costa Rica and Colombia, linking North and South America?</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Seattle is one of two major U.S. cities on an isthmus. Which state capital is the other?</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>In which country can you find the Dardanelles, the Bosporus, and the Sea of Marmara?</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>What is the most widely spoken language in South America?</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Portuguese</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Which two South American countries are landlocked?</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Bolivia and Paraguay</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>In which country is Aconcagua, the highest peak in the Americas?</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Which lake on the Peru–Bolivia border is known as the highest navigable lake in the world?</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Lake Titicaca</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>What is the highest mountain in Papua New Guinea?</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Mount Wilhelm</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>What is the lowest point in Australia, a usually dry salt lake in South Australia?</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Lake Eyre</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>What is Australia's longest river?</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Murray River</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Which sea separates Australia and New Zealand?</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Tasman Sea</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Uluru, the giant sandstone monolith in central Australia, is also known by what English name?</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Ayers Rock</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Which country's Māori name, Aotearoa, means "Land of the Long White Cloud"?</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>How many sovereign countries are there in Oceania?</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through Baghdad?</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Tigris</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through the Russian city of Saint Petersburg?</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Neva</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through the Australian city of Perth?</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Swan River</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows between the "Twin Cities" of Minneapolis and St. Paul?</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Which river flows through the Scottish city of Aberdeen?</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Dee</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Counting its overseas territories, which country has the most time zones?</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>How many time zones are there in the contiguous United States?</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>How many main time zones does Australia have?</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>What is the hottest temperature ever recorded on Earth, in degrees Fahrenheit (Death Valley)?</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>What was the name of the supercontinent that once joined all of Earth's landmasses?</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Pangaea</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>What is the name of the horseshoe-shaped zone of volcanoes and earthquakes around the Pacific Ocean?</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Ring of Fire</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>The Himalayas were formed by the collision of which two tectonic plates?</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Indian and Eurasian plates</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>What is the process that creates new oceanic crust as magma rises at mid-ocean ridges?</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Seafloor spreading</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>A desert is commonly defined as a place that receives fewer than how many inches of precipitation per year?</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>What is the world's largest inland body of water, bordered by Iran, Russia, and Kazakhstan?</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Caspian Sea</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Which sea separates the Arabian Peninsula from northeast Africa?</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Red Sea</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>In what year did Mount St. Helens erupt in Washington State?</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Which is the only South American country with coastlines on both the Pacific Ocean and the Caribbean Sea?</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>What is the world's highest uninterrupted waterfall, located in Venezuela?</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Angel Falls</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>The Galápagos Islands belong to which country?</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Which country borders both the Caspian Sea to the north and the Persian Gulf to the south?</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Who painted The Last Supper?</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Leonardo da Vinci</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Who painted The Creation of Adam?</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Michelangelo</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Who painted The Starry Night?</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Vincent van Gogh</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Which New York museum houses Van Gogh's The Starry Night?</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Museum of Modern Art (MoMA)</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Which Florence gallery houses Botticelli's The Birth of Venus and Primavera?</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Uffizi Gallery</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Which German-American artist painted Washington Crossing the Delaware?</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Emanuel Leutze</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>In what year was Washington Crossing the Delaware painted?</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="n">
+        <v>1851</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Which New York museum owns Washington Crossing the Delaware?</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitan Museum of Art</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>What is the only Leonardo da Vinci painting on public view in the Western Hemisphere?</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Ginevra de' Benci</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Which Washington, D.C. museum houses Leonardo's Ginevra de' Benci?</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>National Gallery of Art</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Which Madrid museum is home to Las Meninas?</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>The Prado</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Which Paris museum displays Van Gogh's The Church at Auvers?</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Musée d'Orsay</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Which museum owns Seurat's A Sunday Afternoon on the Island of La Grande Jatte?</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Art Institute of Chicago</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Who painted A Sunday Afternoon on the Island of La Grande Jatte?</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Georges Seurat</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>What technique of painting with tiny dots of pure color did Georges Seurat pioneer?</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Pointillism</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Who painted The Garden of Earthly Delights?</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Hieronymus Bosch</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Which Italian term, meaning "light-dark," describes strong contrast between light and shadow in a painting?</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Chiaroscuro</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>What term describes Caravaggio's extreme, spotlight-like form of chiaroscuro?</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Tenebrism</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>What Italian term, meaning "to evaporate like smoke," describes the soft, hazy blending of tones in the Mona Lisa?</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Sfumato</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>What is the term for paint applied so thickly that it stands up from the canvas?</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Impasto</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>What painting technique applies water-based pigments onto wet plaster?</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Fresco</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>What is a fresco painted on dry plaster called?</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Fresco secco</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Which Baroque painter fled Rome in 1606 after killing a man in a brawl?</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Caravaggio</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Which Flemish Baroque painter ran a famous studio in Antwerp?</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Peter Paul Rubens</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Which 18th-century style that followed the Baroque is known for pastel colors, asymmetry, and ornate decoration?</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Rococo</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Which American post-WWII movement included Jackson Pollock, Mark Rothko, and Willem de Kooning?</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Expressionism</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Which artist is famous for drip paintings made on canvases laid on the floor?</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Jackson Pollock</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Which artist is known for large canvases of stacked, soft-edged rectangles of color?</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Mark Rothko</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Which art movement included Roy Lichtenstein, Keith Haring, and Andy Warhol?</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Pop Art</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Which artist is known for his images of Campbell's Soup cans and Marilyn Monroe?</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Andy Warhol</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Which Pop artist is known for paintings that mimic comic strips?</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Roy Lichtenstein</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Jackson Pollock's on-the-floor technique was influenced by which Native American art form?</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Navajo sand painting</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Which two artists pioneered Cubism?</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Pablo Picasso and Georges Braque</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Marcel Duchamp's 1917 artwork Fountain is what everyday object?</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Urinal</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>What term did Marcel Duchamp use for ordinary manufactured objects presented as art?</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Readymade</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>What title did Duchamp give his postcard of the Mona Lisa with a mustache and goatee?</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>L.H.O.O.Q.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Which "anti-art" movement arose during World War I and foreshadowed Surrealism?</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Dada</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Who wrote the Surrealist Manifesto?</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>André Breton</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Which Belgian Surrealist painted a pipe above the words "Ceci n'est pas une pipe"?</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>René Magritte</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>What is the title of Magritte's "Ceci n'est pas une pipe" painting?</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>The Treachery of Images</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Who painted The Kiss (1907–1908), famous for its gold leaf?</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Gustav Klimt</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>In which city does Klimt's The Kiss hang, at the Belvedere?</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Gustav Klimt was a founder of which Austrian art movement?</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Vienna Secession</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Which Czech artist is famous for Art Nouveau posters of women with long, flowing hair?</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Alphonse Mucha</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Klimt and Mucha are leading figures of which decorative style from around 1900?</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Art Nouveau</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Klimt's "Golden Period" was inspired by what Byzantine artworks he saw in Ravenna?</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Mosaics</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Which Mexican artist is famous for her self-portraits and was married to Diego Rivera?</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Frida Kahlo</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Which American modernist is known for large flower paintings and New Mexico landscapes?</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Georgia O'Keeffe</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>To the nearest million dollars, what did Georgia O'Keeffe's Jimson Weed/White Flower No. 1 sell for in 2014?</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Which Italian Baroque painter is famous for Judith Slaying Holofernes and other scenes of powerful women?</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Artemisia Gentileschi</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Who painted Arrangement in Grey and Black No. 1, better known by the name of the artist's mother?</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>James McNeill Whistler</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Who painted Nighthawks?</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Edward Hopper</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>In what year did Edward Hopper paint Nighthawks?</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="n">
+        <v>1942</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>How many people are shown inside the diner in Hopper's Nighthawks?</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>What is the full title of Hokusai's most famous woodblock print?</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>The Great Wave off Kanagawa</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Which mountain appears in the background of Hokusai's The Great Wave?</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Mount Fuji</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>What Japanese art genre, meaning "pictures of the floating world," includes The Great Wave?</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Ukiyo-e</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>What imported synthetic blue pigment did Hokusai use in The Great Wave?</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Prussian blue</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>What was the name of Picasso's 1901–1904 phase of somber paintings of poverty?</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Blue Period</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>In what year did Picasso paint Les Demoiselles d'Avignon?</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="n">
+        <v>1907</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>How many women are depicted in Picasso's Les Demoiselles d'Avignon?</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Which Greek goddess is the Venus de Milo believed to depict?</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Aphrodite</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>On which Greek island was the Venus de Milo discovered in 1820?</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Milos</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Which Greek goddess does the Winged Victory of Samothrace depict?</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>What kind of marble, named for a Greek island, were the Venus de Milo and Winged Victory carved from?</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Parian marble</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Which ancient Egyptian sculpture has the body of a lion and the head of a human?</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Great Sphinx of Giza</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Which country gave the Statue of Liberty to the United States?</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>In what year was the Statue of Liberty dedicated?</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="n">
+        <v>1886</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Who sculpted the marble David (1501–1504) displayed in Florence?</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Michelangelo</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Approximately how many feet tall is Michelangelo's David?</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>In what year did Michelangelo begin painting the Sistine Chapel ceiling?</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="n">
+        <v>1508</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>What huge fresco did Michelangelo paint on the Sistine Chapel's altar wall between 1536 and 1541?</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>The Last Judgment</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Which American artist is credited with inventing the mobile sculpture?</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Calder</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Who was the official painter of the French Revolution, known for The Death of Marat?</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Jacques-Louis David</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Which Spanish painter created The Third of May 1808?</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Francisco Goya</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Which French Romantic painter created Liberty Leading the People?</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Eugène Delacroix</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Which French painter is considered the father of Realism?</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Gustave Courbet</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Which anonymous street artist's Girl with Balloon shredded itself right after selling at auction in 2018?</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Banksy</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>What was the partially shredded Girl with Balloon renamed?</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Love Is in the Bin</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Which Japanese artist is known for polka dots and Infinity Mirror Rooms?</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Yayoi Kusama</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Which American artist is famous for his shiny stainless-steel Balloon Dog sculptures?</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Jeff Koons</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Which British artist exhibited a tiger shark preserved in formaldehyde?</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Damien Hirst</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>What Leonardo da Vinci painting is the most expensive ever sold at auction?</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Salvator Mundi</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>To the nearest million dollars, what did Salvator Mundi sell for at Christie's in 2017?</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>In what year was the Mona Lisa stolen from the Louvre?</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>What was the name of the Louvre handyman who stole the Mona Lisa?</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Vincenzo Peruggia</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>To the nearest hundred, how many paintings did Van Gogh produce in his career?</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="n">
+        <v>900</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Which painting is traditionally said to be the only one Van Gogh sold during his lifetime?</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>The Red Vineyard</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>What was the first name of Van Gogh's younger brother, the art dealer who supported him?</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>To the nearest hundred, how many letters did Van Gogh write, mostly to his brother?</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Which Northern Renaissance painter helped popularize oil paint and painted the Arnolfini Portrait?</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Jan van Eyck</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Which Flemish painter is known for village scenes such as The Hunters in the Snow?</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Pieter Bruegel the Elder</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Which Impressionist is best known for his paintings of ballet dancers?</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Edgar Degas</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Which Post-Impressionist, often called the father of modern art, reduced objects to basic geometric shapes?</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Paul Cézanne</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>In what year was the first Impressionist exhibition held in Paris?</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="n">
+        <v>1874</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Which Impressionist painted Luncheon of the Boating Party?</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Pierre-Auguste Renoir</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Which 16th-century artist wrote Lives of the Most Excellent Painters, Sculptors, and Architects?</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Giorgio Vasari</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>A pencil note on Munch's 1893 The Scream reads, "Can only have been painted by a..." what?</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Madman</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>What architectural style of raw, exposed concrete was popular from the 1950s to the 1970s?</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Brutalism</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>word</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>How many metopes (carved stone panels) originally decorated the Parthenon?</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D51"/>
+  <autoFilter ref="A1:E251"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1377,226 +6211,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>https://www.rd.com/list/geography-quiz-101/</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>https://www.mentimeter.com/blog/education/best-geography-quizzes-and-trivia-questions</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>https://quizado.com/blog/geography-trivia-questions-and-answers</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>https://surveymars.com/blog/geography-trivia-questions-and-answers/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>https://surveymars.com/blog/50-extremely-hard-geography-trivia-questions-and-answers/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>https://logiclike.com/en/geography-trivia</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>https://greenlight.com/learning-center/fun-facts/geography-trivia</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eventdex.com/blog/geography-trivia-questions-answers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>https://www.quiztriviagames.com/geography-multiple-choice-questions/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>https://geographyquiz.org/quizzes/world-capitals-quiz/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>https://www.earthsattractions.com/world-capitals-quiz-questions-and-answers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>https://factsinstitute.com/games/geography-trivia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>https://www.watercoolertrivia.com/trivia-questions/geography-trivia-questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>https://www.earthsattractions.com/us-state-trivia-questions-and-answers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>https://www.trivianerd.com/topic/us-states-trivia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>https://travelnoire.com/geography-trivia-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>https://www.britannica.com/quiz/islands-and-archipelagos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>https://www.beelovedcity.com/european-geography-quiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>https://www.earthsattractions.com/asia-trivia-questions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kids-world-travel-guide.com/africa-quiz.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kids-world-travel-guide.com/south-america-quiz.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jetpunk.com/quizzes/south-america-geography-quiz-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>https://www.proprofs.com/quiz-school/topic/australia-and-oceania-geography</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>https://www.collegetransitions.com/blog/geography-trivia-questions-for-kids/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>https://www.funtrivia.com/en/Geography/Rivers-3993.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>https://www.britannica.com/quiz/guess-the-city-by-its-river-quiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>https://www.trivianerd.com/topic/north-america-trivia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>https://lizardpoint.com/geography/mideast-water-quiz.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>https://www.jotform.com/blog/art-trivia-questions/</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>https://www.watercoolertrivia.com/trivia-questions/art-trivia-questions</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>https://www.watercoolertrivia.com/trivia-questions/art-history-trivia-questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>https://www.trivianerd.com/topic/art-trivia</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>https://www.trivianerd.com/topic/renaissance-trivia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>https://kwizzbit.com/art-quiz-questions-and-answers/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>https://nibble-app.com/blog/art-trivia</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>https://quizutopia.com/famous-paintings-trivia-quiz-20-questions-and-answers/</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>https://www.quiztriviagames.com/art-trivia-questions/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>https://healthyhappyimpactful.com/art-trivia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>https://randomtrivia.co/art-history-trivia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>https://quizax.com/500-art-quiz-questions-with-answers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>https://boxofpuns.com/art-trivia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>https://www.theartstory.org/definition/chiaroscuro-tenebrism-sfumato/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>https://www.theartstory.org/movement/dada/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>https://www.theartstory.org/movement/northern-renaissance/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>https://www.theartstory.org/movement/post-impressionism/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.funtrivia.com/quizzes/humanities/art/sculpture.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Sunflowers_(Van_Gogh_series)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Fine art</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>https://www.nationalgallery.org.uk/paintings/vincent-van-gogh-sunflowers</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nighthawks_(Hopper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/The_Kiss_(Klimt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Les_Demoiselles_d'Avignon</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mona_Lisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>https://www.guinnessworldrecords.com/world-records/62456-most-expensive-painting-sold-at-auction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>https://www.khanacademy.org/humanities/ap-art-history/south-east-se-asia/japan-art/a/hokusai-under-the-wave-off-kanagawa-the-great-wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>https://www.okeeffemuseum.org/georgia-okeeffe-frida-kahlo-two-cultures-two-journeys-and-one-era/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>https://www.worldhistory.org/article/1377/disarming-aphrodite-rediscovering-the-venus-de-mil/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>https://www.mentalfloss.com/article/71643/15-things-you-might-not-know-about-michelangelos-david</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>https://insights.masterworks.com/art/artists/how-many-paintings-did-van-gogh-sell/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Fine art</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>https://quizlet.com/79627195/art-exam-4-study-questions-flash-cards/</t>
         </is>
       </c>
     </row>
